--- a/Output/BRDM_countarea_ALM_A46_PLSUVapes.xlsx
+++ b/Output/BRDM_countarea_ALM_A46_PLSUVapes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1789,6 +1789,374 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.352265043948614</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0.7575757575757575</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4901960784313725</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.7589556769884639</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>0.9178943503602737</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.8230452674897119</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>2.439024390243902</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.465201465201465</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1800,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,6 +3529,374 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.352265043948614</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4901960784313726</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7092198581560283</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.758955676988464</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>0.9178943503602737</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.823045267489712</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>1.991455075433478</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.465201465201465</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
